--- a/config/excel/CfgLootPool.xlsx
+++ b/config/excel/CfgLootPool.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootPool" sheetId="1" r:id="Rdbe648f0f59345fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootPool" sheetId="1" r:id="Rcb7f494643b64c70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +36,13 @@
       <x:color rgb="FF0000FF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +57,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -63,7 +101,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -88,6 +126,36 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -301,122 +369,302 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="17" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="17" t="str">
         <x:v>PoolID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="17" t="str">
         <x:v>DefinitionId</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="17" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="17" t="str">
         <x:v>MinLevel</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="17" t="str">
         <x:v>MaxLevel</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="18" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="18" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="18" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="18" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="18" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
+      <x:c r="F2" s="18" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="19" t="str">
         <x:v># 掉落项身份</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="19" t="str">
         <x:v>掉落池身份</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="19" t="str">
         <x:v>物品模板身份</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="19" t="str">
         <x:v>分类抽取权重</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="19" t="str">
         <x:v>最低掉落等级</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="19" t="str">
         <x:v>最高掉落等级</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="9" t="str">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="15" t="str">
         <x:v>weapon</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="str">
+      <x:c r="B4" s="15" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="str">
+      <x:c r="C4" s="15" t="str">
         <x:v>ruin_weapon</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="9" t="str">
+      <x:c r="D4" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="15" t="str">
         <x:v>armor</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="str">
+      <x:c r="B5" s="15" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="str">
+      <x:c r="C5" s="15" t="str">
         <x:v>ruin_armor</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="9" t="str">
+      <x:c r="D5" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="15" t="str">
         <x:v>item</x:v>
       </x:c>
-      <x:c r="B6" s="9" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="str">
+      <x:c r="C6" s="15" t="str">
         <x:v>relic_part</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="3" t="n">
+      <x:c r="D6" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="15" t="str">
+        <x:v>treasure_weapon</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>ruin_weapon</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="15" t="str">
+        <x:v>treasure_armor</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="str">
+        <x:v>ruin_armor</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="15" t="str">
+        <x:v>treasure_item</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="str">
+        <x:v>relic_part</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="15" t="str">
+        <x:v>merchant_weapon</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="str">
+        <x:v>ruin_weapon</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="15" t="str">
+        <x:v>merchant_armor</x:v>
+      </x:c>
+      <x:c r="B11" s="15" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="str">
+        <x:v>ruin_armor</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="15" t="str">
+        <x:v>merchant_item</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="str">
+        <x:v>relic_part</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="15" t="str">
+        <x:v>boss_weapon</x:v>
+      </x:c>
+      <x:c r="B13" s="15" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="str">
+        <x:v>ruin_weapon</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="15" t="str">
+        <x:v>boss_armor</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="str">
+        <x:v>ruin_armor</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="15" t="str">
+        <x:v>boss_item</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="str">
+        <x:v>relic_part</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgLootPool.xlsx
+++ b/config/excel/CfgLootPool.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootPool" sheetId="1" r:id="Rcb7f494643b64c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootPool" sheetId="1" r:id="R5f47a9b22215484c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,6 +41,11 @@
       <x:color rgb="FF215E99"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="11">
     <x:fill>
@@ -101,7 +106,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -158,6 +163,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -360,9 +366,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
@@ -459,7 +465,7 @@
         <x:v>ruin_armor</x:v>
       </x:c>
       <x:c r="D5" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="16" t="n">
         <x:v>1</x:v>
@@ -479,7 +485,7 @@
         <x:v>relic_part</x:v>
       </x:c>
       <x:c r="D6" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="16" t="n">
         <x:v>1</x:v>
@@ -519,7 +525,7 @@
         <x:v>ruin_armor</x:v>
       </x:c>
       <x:c r="D8" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E8" s="16" t="n">
         <x:v>1</x:v>
@@ -539,7 +545,7 @@
         <x:v>relic_part</x:v>
       </x:c>
       <x:c r="D9" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="16" t="n">
         <x:v>1</x:v>
@@ -579,7 +585,7 @@
         <x:v>ruin_armor</x:v>
       </x:c>
       <x:c r="D11" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E11" s="16" t="n">
         <x:v>1</x:v>
@@ -599,7 +605,7 @@
         <x:v>relic_part</x:v>
       </x:c>
       <x:c r="D12" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="16" t="n">
         <x:v>1</x:v>
@@ -639,7 +645,7 @@
         <x:v>ruin_armor</x:v>
       </x:c>
       <x:c r="D14" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="16" t="n">
         <x:v>1</x:v>
@@ -659,12 +665,252 @@
         <x:v>relic_part</x:v>
       </x:c>
       <x:c r="D15" s="16" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="20" t="str">
+        <x:v>default_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B16" s="20" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="20" t="str">
+        <x:v>default_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="20" t="str">
+        <x:v>default_guard_blade</x:v>
+      </x:c>
+      <x:c r="B18" s="20" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" s="20" t="str">
+        <x:v>treasure_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="20" t="str">
+        <x:v>treasure_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B20" s="20" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="20" t="str">
+        <x:v>treasure_guard_blade</x:v>
+      </x:c>
+      <x:c r="B21" s="20" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="20" t="str">
+        <x:v>merchant_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B22" s="20" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="n">
+      <x:c r="E22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="20" t="str">
+        <x:v>merchant_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B23" s="20" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="20" t="str">
+        <x:v>merchant_guard_blade</x:v>
+      </x:c>
+      <x:c r="B24" s="20" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="A25" s="20" t="str">
+        <x:v>boss_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B25" s="20" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="20" t="str">
+        <x:v>boss_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B26" s="20" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="20" t="str">
+        <x:v>boss_guard_blade</x:v>
+      </x:c>
+      <x:c r="B27" s="20" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgLootPool.xlsx
+++ b/config/excel/CfgLootPool.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootPool" sheetId="1" r:id="R5f47a9b22215484c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLootPool" sheetId="1" r:id="Rf9a8f30e28954ddf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47,7 +47,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,6 +92,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -106,7 +121,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -164,6 +179,14 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -366,553 +389,621 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="17" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="22" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="17" t="str">
+      <x:c r="B1" s="22" t="str">
         <x:v>PoolID</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="str">
+      <x:c r="C1" s="22" t="str">
         <x:v>DefinitionId</x:v>
       </x:c>
-      <x:c r="D1" s="17" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="E1" s="17" t="str">
+      <x:c r="E1" s="22" t="str">
         <x:v>MinLevel</x:v>
       </x:c>
-      <x:c r="F1" s="17" t="str">
+      <x:c r="F1" s="22" t="str">
         <x:v>MaxLevel</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="18" t="str">
+      <x:c r="A2" s="23" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" s="18" t="str">
+      <x:c r="B2" s="23" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="18" t="str">
+      <x:c r="C2" s="23" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="str">
+      <x:c r="D2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="18" t="str">
+      <x:c r="E2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="str">
+      <x:c r="F2" s="23" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="56" customHeight="1">
-      <x:c r="A3" s="19" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="25" t="str">
         <x:v># 掉落项身份</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
+      <x:c r="B3" s="25" t="str">
         <x:v>掉落池身份</x:v>
       </x:c>
-      <x:c r="C3" s="19" t="str">
+      <x:c r="C3" s="25" t="str">
         <x:v>物品模板身份</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="str">
+      <x:c r="D3" s="25" t="str">
         <x:v>分类抽取权重</x:v>
       </x:c>
-      <x:c r="E3" s="19" t="str">
+      <x:c r="E3" s="25" t="str">
         <x:v>最低掉落等级</x:v>
       </x:c>
-      <x:c r="F3" s="19" t="str">
+      <x:c r="F3" s="25" t="str">
         <x:v>最高掉落等级</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="36" customHeight="1">
-      <x:c r="A4" s="15" t="str">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="26" t="str">
         <x:v>weapon</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" s="26" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C4" s="15" t="str">
+      <x:c r="C4" s="26" t="str">
         <x:v>ruin_weapon</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="36" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="D4" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="26" t="str">
         <x:v>armor</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" s="26" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="str">
+      <x:c r="C5" s="26" t="str">
         <x:v>ruin_armor</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="n">
+      <x:c r="D5" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="36" customHeight="1">
-      <x:c r="A6" s="15" t="str">
+      <x:c r="E5" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="26" t="str">
         <x:v>item</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="C6" s="15" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>relic_part</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="n">
+      <x:c r="D6" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1">
-      <x:c r="A7" s="15" t="str">
+      <x:c r="E6" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="26" t="str">
         <x:v>treasure_weapon</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str">
+      <x:c r="B7" s="26" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C7" s="15" t="str">
+      <x:c r="C7" s="26" t="str">
         <x:v>ruin_weapon</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="n">
+      <x:c r="D7" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="36" customHeight="1">
-      <x:c r="A8" s="15" t="str">
+      <x:c r="E7" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="26" t="str">
         <x:v>treasure_armor</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str">
+      <x:c r="B8" s="26" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="str">
+      <x:c r="C8" s="26" t="str">
         <x:v>ruin_armor</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="n">
+      <x:c r="D8" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E8" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="36" customHeight="1">
-      <x:c r="A9" s="15" t="str">
+      <x:c r="E8" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="26" t="str">
         <x:v>treasure_item</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="str">
+      <x:c r="B9" s="26" t="str">
         <x:v>treasure</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="str">
+      <x:c r="C9" s="26" t="str">
         <x:v>relic_part</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="n">
+      <x:c r="D9" s="26" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E9" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="36" customHeight="1">
-      <x:c r="A10" s="15" t="str">
+      <x:c r="E9" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="26" t="str">
         <x:v>merchant_weapon</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="str">
+      <x:c r="B10" s="26" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="str">
+      <x:c r="C10" s="26" t="str">
         <x:v>ruin_weapon</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="n">
+      <x:c r="D10" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="36" customHeight="1">
-      <x:c r="A11" s="15" t="str">
+      <x:c r="E10" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="26" t="str">
         <x:v>merchant_armor</x:v>
       </x:c>
-      <x:c r="B11" s="15" t="str">
+      <x:c r="B11" s="26" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="C11" s="26" t="str">
         <x:v>ruin_armor</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="n">
+      <x:c r="D11" s="26" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="36" customHeight="1">
-      <x:c r="A12" s="15" t="str">
+      <x:c r="E11" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="26" t="str">
         <x:v>merchant_item</x:v>
       </x:c>
-      <x:c r="B12" s="15" t="str">
+      <x:c r="B12" s="26" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="C12" s="26" t="str">
         <x:v>relic_part</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="n">
+      <x:c r="D12" s="26" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="36" customHeight="1">
-      <x:c r="A13" s="15" t="str">
-        <x:v>boss_weapon</x:v>
-      </x:c>
-      <x:c r="B13" s="15" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="E12" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="26" t="str">
+        <x:v>default_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B13" s="26" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="26" t="str">
+        <x:v>default_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B14" s="26" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D14" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="26" t="str">
+        <x:v>default_guard_blade</x:v>
+      </x:c>
+      <x:c r="B15" s="26" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D15" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="26" t="str">
+        <x:v>treasure_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B16" s="26" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="26" t="str">
+        <x:v>treasure_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B17" s="26" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D17" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="26" t="str">
+        <x:v>treasure_guard_blade</x:v>
+      </x:c>
+      <x:c r="B18" s="26" t="str">
+        <x:v>treasure</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D18" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="26" t="str">
+        <x:v>merchant_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B19" s="26" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="str">
+        <x:v>ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="D19" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="26" t="str">
+        <x:v>merchant_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B20" s="26" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="str">
+        <x:v>ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="D20" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="26" t="str">
+        <x:v>merchant_guard_blade</x:v>
+      </x:c>
+      <x:c r="B21" s="26" t="str">
+        <x:v>merchant</x:v>
+      </x:c>
+      <x:c r="C21" s="26" t="str">
+        <x:v>guard_blade</x:v>
+      </x:c>
+      <x:c r="D21" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="26" t="str">
+        <x:v>v2_boss_weapon</x:v>
+      </x:c>
+      <x:c r="B22" s="26" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="str">
         <x:v>ruin_weapon</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="n">
+      <x:c r="D22" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="36" customHeight="1">
-      <x:c r="A14" s="15" t="str">
-        <x:v>boss_armor</x:v>
-      </x:c>
-      <x:c r="B14" s="15" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="E22" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="26" t="str">
+        <x:v>v2_boss_armor</x:v>
+      </x:c>
+      <x:c r="B23" s="26" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="str">
         <x:v>ruin_armor</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="n">
+      <x:c r="D23" s="26" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="36" customHeight="1">
-      <x:c r="A15" s="15" t="str">
-        <x:v>boss_item</x:v>
-      </x:c>
-      <x:c r="B15" s="15" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="str">
-        <x:v>relic_part</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="36" customHeight="1">
-      <x:c r="A16" s="20" t="str">
-        <x:v>default_ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="B16" s="20" t="str">
-        <x:v>default</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="str">
+      <x:c r="E23" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="26" t="str">
+        <x:v>v2_boss_ruin_heavy_blade</x:v>
+      </x:c>
+      <x:c r="B24" s="26" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="str">
         <x:v>ruin_heavy_blade</x:v>
       </x:c>
-      <x:c r="D16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="36" customHeight="1">
-      <x:c r="A17" s="20" t="str">
-        <x:v>default_ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="B17" s="20" t="str">
-        <x:v>default</x:v>
-      </x:c>
-      <x:c r="C17" s="20" t="str">
+      <x:c r="D24" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E24" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="26" t="str">
+        <x:v>v2_boss_ruin_poleblade</x:v>
+      </x:c>
+      <x:c r="B25" s="26" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="str">
         <x:v>ruin_poleblade</x:v>
       </x:c>
-      <x:c r="D17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F17" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="36" customHeight="1">
-      <x:c r="A18" s="20" t="str">
-        <x:v>default_guard_blade</x:v>
-      </x:c>
-      <x:c r="B18" s="20" t="str">
-        <x:v>default</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="str">
+      <x:c r="D25" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E25" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="26" t="str">
+        <x:v>v2_boss_guard_blade</x:v>
+      </x:c>
+      <x:c r="B26" s="26" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="str">
         <x:v>guard_blade</x:v>
       </x:c>
-      <x:c r="D18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F18" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="36" customHeight="1">
-      <x:c r="A19" s="20" t="str">
-        <x:v>treasure_ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="B19" s="20" t="str">
-        <x:v>treasure</x:v>
-      </x:c>
-      <x:c r="C19" s="20" t="str">
-        <x:v>ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="D19" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="36" customHeight="1">
-      <x:c r="A20" s="20" t="str">
-        <x:v>treasure_ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="B20" s="20" t="str">
-        <x:v>treasure</x:v>
-      </x:c>
-      <x:c r="C20" s="20" t="str">
-        <x:v>ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="D20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F20" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="36" customHeight="1">
-      <x:c r="A21" s="20" t="str">
-        <x:v>treasure_guard_blade</x:v>
-      </x:c>
-      <x:c r="B21" s="20" t="str">
-        <x:v>treasure</x:v>
-      </x:c>
-      <x:c r="C21" s="20" t="str">
-        <x:v>guard_blade</x:v>
-      </x:c>
-      <x:c r="D21" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F21" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="36" customHeight="1">
-      <x:c r="A22" s="20" t="str">
-        <x:v>merchant_ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="B22" s="20" t="str">
+      <x:c r="D26" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E26" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="26" t="str">
+        <x:v>region_collection</x:v>
+      </x:c>
+      <x:c r="B27" s="26" t="str">
+        <x:v>region_chest</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="str">
+        <x:v>explorer_token</x:v>
+      </x:c>
+      <x:c r="D27" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="26" t="str">
+        <x:v>merchant_collection</x:v>
+      </x:c>
+      <x:c r="B28" s="26" t="str">
         <x:v>merchant</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="D22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F22" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="36" customHeight="1">
-      <x:c r="A23" s="20" t="str">
-        <x:v>merchant_ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="B23" s="20" t="str">
-        <x:v>merchant</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="D23" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F23" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="36" customHeight="1">
-      <x:c r="A24" s="20" t="str">
-        <x:v>merchant_guard_blade</x:v>
-      </x:c>
-      <x:c r="B24" s="20" t="str">
-        <x:v>merchant</x:v>
-      </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>guard_blade</x:v>
-      </x:c>
-      <x:c r="D24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F24" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="36" customHeight="1">
-      <x:c r="A25" s="20" t="str">
-        <x:v>boss_ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="B25" s="20" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C25" s="20" t="str">
-        <x:v>ruin_heavy_blade</x:v>
-      </x:c>
-      <x:c r="D25" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F25" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="36" customHeight="1">
-      <x:c r="A26" s="20" t="str">
-        <x:v>boss_ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="B26" s="20" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C26" s="20" t="str">
-        <x:v>ruin_poleblade</x:v>
-      </x:c>
-      <x:c r="D26" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F26" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="36" customHeight="1">
-      <x:c r="A27" s="20" t="str">
-        <x:v>boss_guard_blade</x:v>
-      </x:c>
-      <x:c r="B27" s="20" t="str">
-        <x:v>boss</x:v>
-      </x:c>
-      <x:c r="C27" s="20" t="str">
-        <x:v>guard_blade</x:v>
-      </x:c>
-      <x:c r="D27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F27" t="n">
-        <x:v>1000</x:v>
-      </x:c>
+      <x:c r="C28" s="26" t="str">
+        <x:v>explorer_token</x:v>
+      </x:c>
+      <x:c r="D28" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F28" s="26" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="26"/>
+      <x:c r="B29" s="26"/>
+      <x:c r="C29" s="26"/>
+      <x:c r="D29" s="26"/>
+      <x:c r="E29" s="26"/>
+      <x:c r="F29" s="26"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="26"/>
+      <x:c r="B30" s="26"/>
+      <x:c r="C30" s="26"/>
+      <x:c r="D30" s="26"/>
+      <x:c r="E30" s="26"/>
+      <x:c r="F30" s="26"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="26"/>
+      <x:c r="B31" s="26"/>
+      <x:c r="C31" s="26"/>
+      <x:c r="D31" s="26"/>
+      <x:c r="E31" s="26"/>
+      <x:c r="F31" s="26"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="26"/>
+      <x:c r="B32" s="26"/>
+      <x:c r="C32" s="26"/>
+      <x:c r="D32" s="26"/>
+      <x:c r="E32" s="26"/>
+      <x:c r="F32" s="26"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="26"/>
+      <x:c r="B33" s="26"/>
+      <x:c r="C33" s="26"/>
+      <x:c r="D33" s="26"/>
+      <x:c r="E33" s="26"/>
+      <x:c r="F33" s="26"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="26"/>
+      <x:c r="B34" s="26"/>
+      <x:c r="C34" s="26"/>
+      <x:c r="D34" s="26"/>
+      <x:c r="E34" s="26"/>
+      <x:c r="F34" s="26"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
